--- a/data/Escenarios_Gx/640kW/elmo_data.xlsx
+++ b/data/Escenarios_Gx/640kW/elmo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\640kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F1BB74-36AE-40EA-9395-7F9D307B065C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF808FF7-3564-4845-A85E-3A4E0019BB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="200">
   <si>
     <t>id</t>
   </si>
@@ -637,6 +637,9 @@
   </si>
   <si>
     <t>0.1</t>
+  </si>
+  <si>
+    <t>h_max</t>
   </si>
 </sst>
 </file>
@@ -710,7 +713,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -993,12 +996,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1215,6 +1229,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5381,13 +5401,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387AF5AC-D97C-4B95-B84B-AE3277E9ED2E}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5412,8 +5432,11 @@
       <c r="H1" s="1" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I1" s="75" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5438,8 +5461,11 @@
       <c r="H2" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="75" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -5463,6 +5489,9 @@
       </c>
       <c r="H3" s="3">
         <v>1000</v>
+      </c>
+      <c r="I3" s="76">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
